--- a/干预措施.xlsx
+++ b/干预措施.xlsx
@@ -1,35 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>cluster_kmeans_bestk</t>
   </si>
@@ -40,19 +29,19 @@
     <t>Adherence</t>
   </si>
   <si>
-    <t>Regimen optimization changes</t>
+    <t xml:space="preserve">Regimen optimization changes</t>
   </si>
   <si>
-    <t>GDMT counts</t>
+    <t xml:space="preserve">GDMT counts</t>
   </si>
   <si>
-    <t>DDI/ADR actions</t>
+    <t xml:space="preserve">DDI/ADR actions</t>
   </si>
   <si>
-    <t>Medication education counts</t>
+    <t xml:space="preserve">Medication education counts</t>
   </si>
   <si>
-    <t>Accepted actions</t>
+    <t xml:space="preserve">Accepted actions</t>
   </si>
   <si>
     <t>mid</t>
@@ -63,170 +52,141 @@
   <si>
     <t>low</t>
   </si>
-  <si>
-    <t>差</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11.000000"/>
+      <color indexed="4"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11.000000"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="18.000000"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="15.000000"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="13.000000"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11.000000"/>
+      <color indexed="65"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -239,198 +199,167 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="26"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.79998168889431398"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.59999389629810496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.39997558519241899"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.79998168889431398"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.59999389629810496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.39997558519241899"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.79998168889431398"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.59999389629810496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.39997558519241899"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.79998168889431398"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.59999389629810496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.39997558519241899"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.79998168889431398"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.59999389629810496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.39997558519241899"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.79998168889431398"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.59999389629810496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.39997558519241899"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="9">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -445,25 +374,25 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -478,7 +407,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -493,7 +422,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="double">
@@ -508,183 +437,183 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="2" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="2" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="3" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="9" fillId="3" borderId="4" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="10" fillId="4" borderId="5" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="11" fillId="4" borderId="4" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="12" fillId="5" borderId="6" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="13" fillId="0" borderId="7" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="14" fillId="0" borderId="8" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="15" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="16" fillId="7" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="17" fillId="8" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="9" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="12" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="13" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="14" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="15" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="16" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="17" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="18" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="19" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="20" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="21" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="22" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="23" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="24" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="25" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="26" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="27" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="28" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="29" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="30" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="31" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="32" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -739,6 +668,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -748,8 +678,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
@@ -792,73 +1005,13 @@
     <a:fontScheme name="WPS">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="WPS">
@@ -961,7 +1114,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -996,15 +1149,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,7 +1185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1056,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1082,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1108,7 +1263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1134,7 +1289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1160,7 +1315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1186,7 +1341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1212,7 +1367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1238,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -1264,7 +1419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11">
       <c r="A11" s="1">
         <v>0</v>
       </c>
@@ -1290,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12">
       <c r="A12" s="1">
         <v>0</v>
       </c>
@@ -1316,7 +1471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13">
       <c r="A13" s="1">
         <v>0</v>
       </c>
@@ -1342,7 +1497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14">
       <c r="A14" s="1">
         <v>0</v>
       </c>
@@ -1368,7 +1523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1394,7 +1549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1420,7 +1575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17">
       <c r="A17" s="1">
         <v>0</v>
       </c>
@@ -1446,7 +1601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18">
       <c r="A18" s="1">
         <v>0</v>
       </c>
@@ -1472,7 +1627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19">
       <c r="A19" s="1">
         <v>0</v>
       </c>
@@ -1498,7 +1653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20">
       <c r="A20" s="1">
         <v>0</v>
       </c>
@@ -1524,7 +1679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21">
       <c r="A21" s="1">
         <v>0</v>
       </c>
@@ -1550,7 +1705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -1576,7 +1731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23">
       <c r="A23" s="1">
         <v>0</v>
       </c>
@@ -1602,7 +1757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1628,7 +1783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -1654,7 +1809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -1680,7 +1835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27">
       <c r="A27" s="1">
         <v>0</v>
       </c>
@@ -1706,7 +1861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -1732,7 +1887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29">
       <c r="A29" s="1">
         <v>0</v>
       </c>
@@ -1758,7 +1913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30">
       <c r="A30" s="1">
         <v>0</v>
       </c>
@@ -1784,7 +1939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -1810,7 +1965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1836,7 +1991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33">
       <c r="A33" s="1">
         <v>0</v>
       </c>
@@ -1862,7 +2017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34">
       <c r="A34" s="1">
         <v>1</v>
       </c>
@@ -1888,7 +2043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -1914,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36">
       <c r="A36" s="1">
         <v>0</v>
       </c>
@@ -1940,7 +2095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37">
       <c r="A37" s="1">
         <v>1</v>
       </c>
@@ -1966,7 +2121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38">
       <c r="A38" s="1">
         <v>0</v>
       </c>
@@ -1992,7 +2147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -2018,7 +2173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -2044,7 +2199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41">
       <c r="A41" s="1">
         <v>0</v>
       </c>
@@ -2070,7 +2225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42">
       <c r="A42" s="1">
         <v>1</v>
       </c>
@@ -2096,7 +2251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43">
       <c r="A43" s="1">
         <v>1</v>
       </c>
@@ -2122,7 +2277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44">
       <c r="A44" s="1">
         <v>1</v>
       </c>
@@ -2148,7 +2303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45">
       <c r="A45" s="1">
         <v>1</v>
       </c>
@@ -2174,7 +2329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46">
       <c r="A46" s="1">
         <v>0</v>
       </c>
@@ -2200,7 +2355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47">
       <c r="A47" s="1">
         <v>0</v>
       </c>
@@ -2226,7 +2381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48">
       <c r="A48" s="1">
         <v>0</v>
       </c>
@@ -2252,7 +2407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49">
       <c r="A49" s="1">
         <v>0</v>
       </c>
@@ -2278,7 +2433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50">
       <c r="A50" s="1">
         <v>0</v>
       </c>
@@ -2304,7 +2459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -2330,7 +2485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52">
       <c r="A52" s="1">
         <v>0</v>
       </c>
@@ -2356,7 +2511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53">
       <c r="A53" s="1">
         <v>0</v>
       </c>
@@ -2382,7 +2537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54">
       <c r="A54" s="1">
         <v>1</v>
       </c>
@@ -2408,7 +2563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55">
       <c r="A55" s="1">
         <v>0</v>
       </c>
@@ -2434,7 +2589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56">
       <c r="A56" s="1">
         <v>1</v>
       </c>
@@ -2460,7 +2615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57">
       <c r="A57" s="1">
         <v>1</v>
       </c>
@@ -2486,7 +2641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58">
       <c r="A58" s="1">
         <v>1</v>
       </c>
@@ -2512,7 +2667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59">
       <c r="A59" s="1">
         <v>1</v>
       </c>
@@ -2538,7 +2693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60">
       <c r="A60" s="1">
         <v>1</v>
       </c>
@@ -2564,7 +2719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61">
       <c r="A61" s="1">
         <v>0</v>
       </c>
@@ -2590,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62">
       <c r="A62" s="1">
         <v>1</v>
       </c>
@@ -2616,7 +2771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63">
       <c r="A63" s="1">
         <v>0</v>
       </c>
@@ -2642,7 +2797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64">
       <c r="A64" s="1">
         <v>1</v>
       </c>
@@ -2668,7 +2823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65">
       <c r="A65" s="1">
         <v>0</v>
       </c>
@@ -2694,7 +2849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66">
       <c r="A66" s="1">
         <v>0</v>
       </c>
@@ -2720,7 +2875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67">
       <c r="A67" s="1">
         <v>1</v>
       </c>
@@ -2746,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68">
       <c r="A68" s="1">
         <v>0</v>
       </c>
@@ -2772,7 +2927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69">
       <c r="A69" s="1">
         <v>1</v>
       </c>
@@ -2798,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70">
       <c r="A70" s="1">
         <v>1</v>
       </c>
@@ -2806,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2824,15 +2979,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71">
       <c r="A71" s="1">
         <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2850,7 +3005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72">
       <c r="A72" s="1">
         <v>1</v>
       </c>
@@ -2858,7 +3013,7 @@
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2876,7 +3031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73">
       <c r="A73" s="1">
         <v>1</v>
       </c>
@@ -2902,7 +3057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74">
       <c r="A74" s="1">
         <v>1</v>
       </c>
@@ -2928,7 +3083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75">
       <c r="A75" s="1">
         <v>0</v>
       </c>
@@ -2954,7 +3109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76">
       <c r="A76" s="1">
         <v>0</v>
       </c>
@@ -2980,7 +3135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77">
       <c r="A77" s="1">
         <v>1</v>
       </c>
@@ -3006,7 +3161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78">
       <c r="A78" s="1">
         <v>1</v>
       </c>
@@ -3032,7 +3187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79">
       <c r="A79" s="1">
         <v>1</v>
       </c>
@@ -3058,7 +3213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80">
       <c r="A80" s="1">
         <v>0</v>
       </c>
@@ -3084,7 +3239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81">
       <c r="A81" s="1">
         <v>1</v>
       </c>
@@ -3110,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82">
       <c r="A82" s="1">
         <v>1</v>
       </c>
@@ -3136,7 +3291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83">
       <c r="A83" s="1">
         <v>1</v>
       </c>
@@ -3162,7 +3317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84">
       <c r="A84" s="1">
         <v>1</v>
       </c>
@@ -3188,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85">
       <c r="A85" s="1">
         <v>1</v>
       </c>
@@ -3214,7 +3369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86">
       <c r="A86" s="1">
         <v>0</v>
       </c>
@@ -3240,7 +3395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87">
       <c r="A87" s="1">
         <v>1</v>
       </c>
@@ -3266,7 +3421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88">
       <c r="A88" s="1">
         <v>1</v>
       </c>
@@ -3292,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89">
       <c r="A89" s="1">
         <v>1</v>
       </c>
@@ -3318,7 +3473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90">
       <c r="A90" s="1">
         <v>1</v>
       </c>
@@ -3344,7 +3499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91">
       <c r="A91" s="1">
         <v>0</v>
       </c>
@@ -3370,7 +3525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92">
       <c r="A92" s="1">
         <v>1</v>
       </c>
@@ -3396,7 +3551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93">
       <c r="A93" s="1">
         <v>1</v>
       </c>
@@ -3422,7 +3577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94">
       <c r="A94" s="1">
         <v>0</v>
       </c>
@@ -3448,7 +3603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95">
       <c r="A95" s="1">
         <v>1</v>
       </c>
@@ -3474,7 +3629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96">
       <c r="A96" s="1">
         <v>1</v>
       </c>
@@ -3500,7 +3655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97">
       <c r="A97" s="1">
         <v>1</v>
       </c>
@@ -3526,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98">
       <c r="A98" s="1">
         <v>0</v>
       </c>
@@ -3553,32 +3708,39 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>